--- a/Docs/ParaBank Documentation.xlsx
+++ b/Docs/ParaBank Documentation.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="473">
   <si>
     <t>PARABANK PLAYWRIGHT AUTOMATION — TEST PLAN</t>
   </si>
@@ -1474,6 +1474,24 @@
     <t>Investigating</t>
   </si>
   <si>
+    <t>BR-006</t>
+  </si>
+  <si>
+    <t>Negative alance transferr</t>
+  </si>
+  <si>
+    <t>BR-007</t>
+  </si>
+  <si>
+    <t>More balance than current current balance tranfer</t>
+  </si>
+  <si>
+    <t>BR-008</t>
+  </si>
+  <si>
+    <t>Same account money transfer</t>
+  </si>
+  <si>
     <t>FINAL TEST SUMMARY REPORT</t>
   </si>
   <si>
@@ -1499,12 +1517,6 @@
   </si>
   <si>
     <t>Total Defects Logged</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>3</t>
@@ -1631,7 +1643,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1652,6 +1664,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4148,7 +4163,18 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="26" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="14.29"/>
+    <col customWidth="1" min="2" max="2" width="8.71"/>
+    <col customWidth="1" min="3" max="3" width="16.71"/>
+    <col customWidth="1" min="4" max="4" width="26.29"/>
+    <col customWidth="1" min="5" max="5" width="45.14"/>
+    <col customWidth="1" min="6" max="6" width="22.14"/>
+    <col customWidth="1" min="7" max="7" width="40.86"/>
+    <col customWidth="1" min="8" max="8" width="24.86"/>
+    <col customWidth="1" min="9" max="9" width="43.29"/>
+    <col customWidth="1" min="10" max="10" width="8.71"/>
+    <col customWidth="1" min="11" max="11" width="15.29"/>
+    <col customWidth="1" min="12" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6730,7 +6756,18 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="26" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="14.29"/>
+    <col customWidth="1" min="2" max="2" width="14.43"/>
+    <col customWidth="1" min="3" max="3" width="12.86"/>
+    <col customWidth="1" min="4" max="4" width="35.57"/>
+    <col customWidth="1" min="5" max="5" width="30.29"/>
+    <col customWidth="1" min="6" max="6" width="24.43"/>
+    <col customWidth="1" min="7" max="7" width="34.57"/>
+    <col customWidth="1" min="8" max="8" width="20.14"/>
+    <col customWidth="1" min="9" max="9" width="40.71"/>
+    <col customWidth="1" min="10" max="10" width="20.86"/>
+    <col customWidth="1" min="11" max="11" width="15.57"/>
+    <col customWidth="1" min="12" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10523,7 +10560,7 @@
         <v>403</v>
       </c>
       <c r="B6" s="3">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="7">
@@ -10531,7 +10568,7 @@
         <v>404</v>
       </c>
       <c r="B7" s="3">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="8">
@@ -11700,6 +11737,48 @@
         <v>436</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -12701,12 +12780,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>398</v>
@@ -12714,31 +12793,31 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="B7" s="3">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="B8" s="3">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="9">
@@ -12746,7 +12825,7 @@
         <v>404</v>
       </c>
       <c r="B9" s="3">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="10">
@@ -12767,118 +12846,125 @@
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>446</v>
+        <v>451</v>
+      </c>
+      <c r="B14" s="3">
+        <v>8.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>447</v>
+      <c r="A15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="s">
-        <v>449</v>
+      <c r="B17" s="9" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
+      <c r="A19" s="8" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="8" t="s">
-        <v>464</v>
-      </c>
-    </row>
+        <v>465</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="B30" s="2" t="s">
+      <c r="A28" s="8" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
     <row r="32" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -13847,6 +13933,7 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
